--- a/artfynd/A 50404-2023 artfynd.xlsx
+++ b/artfynd/A 50404-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50404-2023 artfynd.xlsx
+++ b/artfynd/A 50404-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90852028</v>
+        <v>95465673</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>linghem-Backeby, Ög</t>
+          <t>Linköpings kommun - projekt Ostlänken naturvärdesinventering 2021, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546378.1759559793</v>
+        <v>546324</v>
       </c>
       <c r="R2" t="n">
-        <v>6480574.904919279</v>
+        <v>6480494</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Åtminstone 4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,39 +766,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Hanna Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Lingham- Bäckeby - Greensway AB</t>
-        </is>
-      </c>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95465673</v>
+        <v>90852028</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linköpings kommun - projekt Ostlänken naturvärdesinventering 2021, Ög</t>
+          <t>linghem-Backeby, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546324.0983397185</v>
+        <v>546378</v>
       </c>
       <c r="R3" t="n">
-        <v>6480493.692786826</v>
+        <v>6480575</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Åtminstone 4 fruktkroppar</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,18 +863,27 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Lingham- Bäckeby - Greensway AB</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50404-2023 artfynd.xlsx
+++ b/artfynd/A 50404-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95465673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
           <t>Lingham- Bäckeby - Greensway AB</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90852028</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>